--- a/site/leagues/betclic/2026_2027/xlsx/context_packs/context_pack_ADO.xlsx
+++ b/site/leagues/betclic/2026_2027/xlsx/context_packs/context_pack_ADO.xlsx
@@ -17,12 +17,12 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'overview'!$A$1:$C$14</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'context_alerts'!$A$1:$B$3</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'team_splits'!$A$1:$I$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'context_alerts'!$A$1:$B$4</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'team_splits'!$A$1:$I$3</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'key_players_context'!$A$1:$M$9</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'team_periods'!$A$1:$K$5</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'key_players_periods'!$A$1:$Q$9</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'game_log'!$A$1:$G$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'game_log'!$A$1:$G$3</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -498,7 +498,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5">
@@ -513,7 +513,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6">
@@ -561,7 +561,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>96.0</t>
+          <t>91.5</t>
         </is>
       </c>
     </row>
@@ -578,7 +578,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>83.0</t>
+          <t>77.0</t>
         </is>
       </c>
     </row>
@@ -595,7 +595,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>13.0</t>
+          <t>14.5</t>
         </is>
       </c>
     </row>
@@ -627,7 +627,11 @@
           <t>diff_fora</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr"/>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>16.0</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -642,7 +646,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Q2 (17)</t>
+          <t>Q3 (12)</t>
         </is>
       </c>
     </row>
@@ -659,7 +663,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Q4 (-14)</t>
+          <t>Q4 (-9)</t>
         </is>
       </c>
     </row>
@@ -675,11 +679,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B3"/>
+  <dimension ref="A1:B4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="25" customWidth="1" min="2" max="2"/>
+    <col width="11" customWidth="1" min="1" max="1"/>
+    <col width="32" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -697,12 +701,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>períodos</t>
+          <t>home/away</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Melhor período: Q2 (17)</t>
+          <t>Diff médio casa: 13 | fora: 16</t>
         </is>
       </c>
     </row>
@@ -714,12 +718,24 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Pior período: Q4 (-14)</t>
+          <t>Melhor período: Q3 (12)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>períodos</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Pior período: Q4 (-9)</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:B3"/>
+  <autoFilter ref="A1:B4"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -730,7 +746,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I2"/>
+  <dimension ref="A1:I3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -794,7 +810,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Home</t>
+          <t>Away</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -806,26 +822,59 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
+        <v>87</v>
+      </c>
+      <c r="E2" t="n">
+        <v>71</v>
+      </c>
+      <c r="F2" t="n">
+        <v>16</v>
+      </c>
+      <c r="G2" t="n">
+        <v>87</v>
+      </c>
+      <c r="H2" t="n">
+        <v>71</v>
+      </c>
+      <c r="I2" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Home</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D3" t="n">
         <v>96</v>
       </c>
-      <c r="E2" t="n">
+      <c r="E3" t="n">
         <v>83</v>
       </c>
-      <c r="F2" t="n">
+      <c r="F3" t="n">
         <v>13</v>
       </c>
-      <c r="G2" t="n">
+      <c r="G3" t="n">
         <v>96</v>
       </c>
-      <c r="H2" t="n">
+      <c r="H3" t="n">
         <v>83</v>
       </c>
-      <c r="I2" t="n">
+      <c r="I3" t="n">
         <v>13</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I2"/>
+  <autoFilter ref="A1:I3"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -924,30 +973,38 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>L. Ayers</t>
+          <t>R. Woods</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>23.2</v>
+        <v>18.2</v>
       </c>
       <c r="C2" t="n">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="D2" t="n">
+        <v>9</v>
+      </c>
+      <c r="E2" t="n">
+        <v>22.8</v>
+      </c>
+      <c r="F2" t="n">
+        <v>2</v>
+      </c>
+      <c r="G2" t="n">
+        <v>17</v>
+      </c>
+      <c r="H2" t="n">
         <v>8</v>
       </c>
-      <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr"/>
-      <c r="G2" t="inlineStr"/>
-      <c r="H2" t="n">
-        <v>23</v>
-      </c>
       <c r="I2" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
+      <c r="L2" t="n">
+        <v>12</v>
+      </c>
       <c r="M2" t="inlineStr"/>
     </row>
     <row r="3">
@@ -965,163 +1022,211 @@
       <c r="D3" t="n">
         <v>12</v>
       </c>
-      <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr"/>
-      <c r="G3" t="inlineStr"/>
+      <c r="E3" t="n">
+        <v>23.8</v>
+      </c>
+      <c r="F3" t="n">
+        <v>9</v>
+      </c>
+      <c r="G3" t="n">
+        <v>-7</v>
+      </c>
       <c r="H3" t="n">
-        <v>16</v>
+        <v>12.5</v>
       </c>
       <c r="I3" t="n">
-        <v>12</v>
+        <v>2.5</v>
       </c>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
+      <c r="L3" t="n">
+        <v>7</v>
+      </c>
       <c r="M3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>R. Woods</t>
+          <t>N. Morais</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>18.2</v>
+        <v>17.6</v>
       </c>
       <c r="C4" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="D4" t="n">
-        <v>9</v>
-      </c>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr"/>
-      <c r="G4" t="inlineStr"/>
+        <v>16</v>
+      </c>
+      <c r="E4" t="n">
+        <v>17.2</v>
+      </c>
+      <c r="F4" t="n">
+        <v>3</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0</v>
+      </c>
       <c r="H4" t="n">
-        <v>14</v>
+        <v>5.5</v>
       </c>
       <c r="I4" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
+      <c r="L4" t="n">
+        <v>5</v>
+      </c>
       <c r="M4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>J. Palm</t>
+          <t>L. Boyle</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>25.7</v>
+        <v>24.7</v>
       </c>
       <c r="C5" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D5" t="n">
-        <v>-1</v>
-      </c>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr"/>
+        <v>19</v>
+      </c>
+      <c r="E5" t="n">
+        <v>16.2</v>
+      </c>
+      <c r="F5" t="n">
+        <v>5</v>
+      </c>
+      <c r="G5" t="n">
+        <v>20</v>
+      </c>
       <c r="H5" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="I5" t="n">
-        <v>-1</v>
+        <v>19.5</v>
       </c>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
+      <c r="L5" t="n">
+        <v>4</v>
+      </c>
       <c r="M5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>L. Boyle</t>
+          <t>M. Monteiro</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>24.7</v>
+        <v>21.6</v>
       </c>
       <c r="C6" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="D6" t="n">
-        <v>19</v>
-      </c>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr"/>
+        <v>20</v>
+      </c>
+      <c r="E6" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="F6" t="n">
+        <v>6</v>
+      </c>
+      <c r="G6" t="n">
+        <v>4</v>
+      </c>
       <c r="H6" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="I6" t="n">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
+      <c r="L6" t="n">
+        <v>-2</v>
+      </c>
       <c r="M6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>J. Wood</t>
+          <t>L. Ayers</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>18.5</v>
+        <v>23.2</v>
       </c>
       <c r="C7" t="n">
-        <v>7</v>
+        <v>23</v>
       </c>
       <c r="D7" t="n">
-        <v>6</v>
-      </c>
-      <c r="E7" t="inlineStr"/>
-      <c r="F7" t="inlineStr"/>
-      <c r="G7" t="inlineStr"/>
+        <v>8</v>
+      </c>
+      <c r="E7" t="n">
+        <v>29.3</v>
+      </c>
+      <c r="F7" t="n">
+        <v>26</v>
+      </c>
+      <c r="G7" t="n">
+        <v>21</v>
+      </c>
       <c r="H7" t="n">
-        <v>7</v>
+        <v>24.5</v>
       </c>
       <c r="I7" t="n">
-        <v>6</v>
+        <v>14.5</v>
       </c>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
+      <c r="L7" t="n">
+        <v>-3</v>
+      </c>
       <c r="M7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>M. Monteiro</t>
+          <t>J. Wood</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>21.6</v>
+        <v>18.5</v>
       </c>
       <c r="C8" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D8" t="n">
-        <v>20</v>
-      </c>
-      <c r="E8" t="inlineStr"/>
-      <c r="F8" t="inlineStr"/>
-      <c r="G8" t="inlineStr"/>
+        <v>6</v>
+      </c>
+      <c r="E8" t="n">
+        <v>22</v>
+      </c>
+      <c r="F8" t="n">
+        <v>12</v>
+      </c>
+      <c r="G8" t="n">
+        <v>11</v>
+      </c>
       <c r="H8" t="n">
-        <v>4</v>
+        <v>9.5</v>
       </c>
       <c r="I8" t="n">
-        <v>20</v>
+        <v>8.5</v>
       </c>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
+      <c r="L8" t="n">
+        <v>-5</v>
+      </c>
       <c r="M8" t="inlineStr"/>
     </row>
     <row r="9">
@@ -1139,18 +1244,26 @@
       <c r="D9" t="n">
         <v>0</v>
       </c>
-      <c r="E9" t="inlineStr"/>
-      <c r="F9" t="inlineStr"/>
-      <c r="G9" t="inlineStr"/>
+      <c r="E9" t="n">
+        <v>23.4</v>
+      </c>
+      <c r="F9" t="n">
+        <v>10</v>
+      </c>
+      <c r="G9" t="n">
+        <v>1</v>
+      </c>
       <c r="H9" t="n">
-        <v>3</v>
+        <v>6.5</v>
       </c>
       <c r="I9" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
+      <c r="L9" t="n">
+        <v>-7</v>
+      </c>
       <c r="M9" t="inlineStr"/>
     </row>
   </sheetData>
@@ -1260,25 +1373,25 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F2" t="n">
-        <v>26</v>
+        <v>43</v>
       </c>
       <c r="G2" t="n">
-        <v>19</v>
+        <v>40</v>
       </c>
       <c r="H2" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="I2" t="n">
-        <v>26</v>
+        <v>21.5</v>
       </c>
       <c r="J2" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K2" t="n">
-        <v>7</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="3">
@@ -1303,25 +1416,25 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F3" t="n">
+        <v>46</v>
+      </c>
+      <c r="G3" t="n">
         <v>26</v>
       </c>
-      <c r="G3" t="n">
-        <v>9</v>
-      </c>
       <c r="H3" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="I3" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="J3" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="K3" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
     </row>
     <row r="4">
@@ -1346,25 +1459,25 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F4" t="n">
-        <v>23</v>
+        <v>53</v>
       </c>
       <c r="G4" t="n">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="H4" t="n">
-        <v>3</v>
+        <v>24</v>
       </c>
       <c r="I4" t="n">
-        <v>23</v>
+        <v>26.5</v>
       </c>
       <c r="J4" t="n">
-        <v>20</v>
+        <v>14.5</v>
       </c>
       <c r="K4" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
     </row>
     <row r="5">
@@ -1389,25 +1502,25 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F5" t="n">
-        <v>21</v>
+        <v>41</v>
       </c>
       <c r="G5" t="n">
-        <v>35</v>
+        <v>59</v>
       </c>
       <c r="H5" t="n">
-        <v>-14</v>
+        <v>-18</v>
       </c>
       <c r="I5" t="n">
-        <v>21</v>
+        <v>20.5</v>
       </c>
       <c r="J5" t="n">
-        <v>35</v>
+        <v>29.5</v>
       </c>
       <c r="K5" t="n">
-        <v>-14</v>
+        <v>-9</v>
       </c>
     </row>
   </sheetData>
@@ -1538,40 +1651,40 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E2" t="n">
-        <v>3</v>
+        <v>1.5</v>
       </c>
       <c r="F2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G2" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="H2" t="n">
         <v>2</v>
       </c>
-      <c r="H2" t="n">
-        <v>0</v>
-      </c>
       <c r="I2" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="J2" t="n">
         <v>0</v>
       </c>
       <c r="K2" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="L2" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="M2" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="N2" t="n">
         <v>1</v>
@@ -1580,10 +1693,10 @@
         <v>0</v>
       </c>
       <c r="P2" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="Q2" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="3">
@@ -1593,22 +1706,22 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>3</v>
+        <v>1.5</v>
       </c>
       <c r="C3" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="E3" t="n">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="F3" t="n">
-        <v>2</v>
+        <v>3.5</v>
       </c>
       <c r="G3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H3" t="n">
         <v>3</v>
@@ -1623,74 +1736,74 @@
         <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="M3" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="P3" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="Q3" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>R. Woods</t>
+          <t>J. Wood</t>
         </is>
       </c>
       <c r="B4" t="n">
+        <v>1</v>
+      </c>
+      <c r="C4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D4" t="n">
         <v>6</v>
       </c>
-      <c r="C4" t="n">
+      <c r="E4" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H4" t="n">
         <v>2</v>
       </c>
-      <c r="D4" t="n">
-        <v>0</v>
-      </c>
-      <c r="E4" t="n">
-        <v>6</v>
-      </c>
-      <c r="F4" t="n">
-        <v>1</v>
-      </c>
-      <c r="G4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H4" t="n">
-        <v>0</v>
-      </c>
       <c r="I4" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="J4" t="n">
         <v>0</v>
       </c>
       <c r="K4" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
@@ -1699,26 +1812,26 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>J. Palm</t>
+          <t>R. Soeiro</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="C5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D5" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E5" t="n">
-        <v>5</v>
+        <v>1.5</v>
       </c>
       <c r="F5" t="n">
-        <v>1</v>
+        <v>2.5</v>
       </c>
       <c r="G5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H5" t="n">
         <v>1</v>
@@ -1727,53 +1840,53 @@
         <v>1</v>
       </c>
       <c r="J5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K5" t="n">
         <v>1</v>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="M5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="O5" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="P5" t="n">
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>L. Boyle</t>
+          <t>R. Woods</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E6" t="n">
+        <v>4</v>
+      </c>
+      <c r="F6" t="n">
         <v>1</v>
       </c>
-      <c r="F6" t="n">
-        <v>0</v>
-      </c>
       <c r="G6" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="H6" t="n">
         <v>0</v>
@@ -1785,19 +1898,19 @@
         <v>1</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N6" t="n">
         <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="P6" t="n">
         <v>0</v>
@@ -1809,36 +1922,36 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>J. Wood</t>
+          <t>L. Boyle</t>
         </is>
       </c>
       <c r="B7" t="n">
         <v>2</v>
       </c>
       <c r="C7" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="D7" t="n">
         <v>3</v>
       </c>
       <c r="E7" t="n">
-        <v>2</v>
+        <v>0.5</v>
       </c>
       <c r="F7" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="G7" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J7" t="n">
         <v>1</v>
       </c>
-      <c r="H7" t="n">
-        <v>2</v>
-      </c>
-      <c r="I7" t="n">
-        <v>0</v>
-      </c>
-      <c r="J7" t="n">
-        <v>0</v>
-      </c>
       <c r="K7" t="n">
         <v>0</v>
       </c>
@@ -1849,13 +1962,13 @@
         <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
@@ -1864,14 +1977,14 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>M. Monteiro</t>
+          <t>N. Morais</t>
         </is>
       </c>
       <c r="B8" t="n">
         <v>1</v>
       </c>
       <c r="C8" t="n">
-        <v>3</v>
+        <v>4.5</v>
       </c>
       <c r="D8" t="n">
         <v>0</v>
@@ -1880,37 +1993,37 @@
         <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="H8" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="I8" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="J8" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="L8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
@@ -1919,45 +2032,53 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>R. Soeiro</t>
+          <t>M. Monteiro</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0</v>
-      </c>
-      <c r="C9" t="inlineStr"/>
+        <v>0.5</v>
+      </c>
+      <c r="C9" t="n">
+        <v>3.5</v>
+      </c>
       <c r="D9" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E9" t="n">
         <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>4</v>
-      </c>
-      <c r="G9" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.5</v>
+      </c>
       <c r="H9" t="n">
         <v>1</v>
       </c>
       <c r="I9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J9" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L9" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="M9" t="n">
         <v>2</v>
       </c>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="n">
-        <v>1</v>
-      </c>
-      <c r="M9" t="n">
-        <v>0</v>
-      </c>
       <c r="N9" t="n">
-        <v>0</v>
-      </c>
-      <c r="O9" t="inlineStr"/>
+        <v>0.5</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0.5</v>
+      </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
@@ -1975,7 +2096,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G2"/>
+  <dimension ref="A1:G3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -2053,8 +2174,37 @@
         <v>13</v>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2922723</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Vitória Sport Clube</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Away</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>87</v>
+      </c>
+      <c r="F3" t="n">
+        <v>71</v>
+      </c>
+      <c r="G3" t="n">
+        <v>16</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:G2"/>
+  <autoFilter ref="A1:G3"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/site/leagues/betclic/2026_2027/xlsx/context_packs/context_pack_ADO.xlsx
+++ b/site/leagues/betclic/2026_2027/xlsx/context_packs/context_pack_ADO.xlsx
@@ -22,7 +22,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'key_players_context'!$A$1:$M$9</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'team_periods'!$A$1:$K$5</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'key_players_periods'!$A$1:$Q$9</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'game_log'!$A$1:$G$3</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'game_log'!$A$1:$G$4</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -498,7 +498,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5">
@@ -513,7 +513,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6">
@@ -561,7 +561,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>91.5</t>
+          <t>87.0</t>
         </is>
       </c>
     </row>
@@ -578,7 +578,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>77.0</t>
+          <t>73.5</t>
         </is>
       </c>
     </row>
@@ -595,7 +595,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>14.5</t>
+          <t>13.5</t>
         </is>
       </c>
     </row>
@@ -612,7 +612,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>13.0</t>
+          <t>11.0</t>
         </is>
       </c>
     </row>
@@ -646,7 +646,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Q3 (12)</t>
+          <t>Q3 (8.7)</t>
         </is>
       </c>
     </row>
@@ -663,7 +663,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Q4 (-9)</t>
+          <t>Q4 (-6.3)</t>
         </is>
       </c>
     </row>
@@ -706,7 +706,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Diff médio casa: 13 | fora: 16</t>
+          <t>Diff médio casa: 11 | fora: 16</t>
         </is>
       </c>
     </row>
@@ -718,7 +718,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Melhor período: Q3 (12)</t>
+          <t>Melhor período: Q3 (8.7)</t>
         </is>
       </c>
     </row>
@@ -730,7 +730,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Pior período: Q4 (-9)</t>
+          <t>Pior período: Q4 (-6.3)</t>
         </is>
       </c>
     </row>
@@ -852,25 +852,25 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D3" t="n">
-        <v>96</v>
+        <v>174</v>
       </c>
       <c r="E3" t="n">
-        <v>83</v>
+        <v>152</v>
       </c>
       <c r="F3" t="n">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="G3" t="n">
-        <v>96</v>
+        <v>87</v>
       </c>
       <c r="H3" t="n">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="I3" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
   </sheetData>
@@ -977,13 +977,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>18.2</v>
+        <v>18.3</v>
       </c>
       <c r="C2" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="D2" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E2" t="n">
         <v>22.8</v>
@@ -995,163 +995,163 @@
         <v>17</v>
       </c>
       <c r="H2" t="n">
-        <v>8</v>
+        <v>7.3</v>
       </c>
       <c r="I2" t="n">
-        <v>13</v>
+        <v>10.3</v>
       </c>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="M2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>D. Cambridge</t>
+          <t>N. Morais</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>23.6</v>
+        <v>16.9</v>
       </c>
       <c r="C3" t="n">
-        <v>16</v>
+        <v>8.5</v>
       </c>
       <c r="D3" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E3" t="n">
-        <v>23.8</v>
+        <v>17.2</v>
       </c>
       <c r="F3" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="G3" t="n">
-        <v>-7</v>
+        <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>12.5</v>
+        <v>6.7</v>
       </c>
       <c r="I3" t="n">
-        <v>2.5</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="n">
-        <v>7</v>
+        <v>5.5</v>
       </c>
       <c r="M3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>N. Morais</t>
+          <t>D. Cambridge</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>17.6</v>
+        <v>23.7</v>
       </c>
       <c r="C4" t="n">
-        <v>8</v>
+        <v>12.5</v>
       </c>
       <c r="D4" t="n">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="E4" t="n">
-        <v>17.2</v>
+        <v>23.8</v>
       </c>
       <c r="F4" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="G4" t="n">
-        <v>0</v>
+        <v>-7</v>
       </c>
       <c r="H4" t="n">
-        <v>5.5</v>
+        <v>11.3</v>
       </c>
       <c r="I4" t="n">
-        <v>8</v>
+        <v>3.7</v>
       </c>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="n">
-        <v>5</v>
+        <v>3.5</v>
       </c>
       <c r="M4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>L. Boyle</t>
+          <t>M. Monteiro</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>24.7</v>
+        <v>21.6</v>
       </c>
       <c r="C5" t="n">
-        <v>9</v>
+        <v>6.5</v>
       </c>
       <c r="D5" t="n">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="E5" t="n">
-        <v>16.2</v>
+        <v>16.7</v>
       </c>
       <c r="F5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G5" t="n">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="H5" t="n">
-        <v>7</v>
+        <v>6.3</v>
       </c>
       <c r="I5" t="n">
-        <v>19.5</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="n">
-        <v>4</v>
+        <v>0.5</v>
       </c>
       <c r="M5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>M. Monteiro</t>
+          <t>L. Boyle</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>21.6</v>
+        <v>20.1</v>
       </c>
       <c r="C6" t="n">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="D6" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="E6" t="n">
+        <v>16.2</v>
+      </c>
+      <c r="F6" t="n">
+        <v>5</v>
+      </c>
+      <c r="G6" t="n">
         <v>20</v>
       </c>
-      <c r="E6" t="n">
-        <v>16.7</v>
-      </c>
-      <c r="F6" t="n">
-        <v>6</v>
-      </c>
-      <c r="G6" t="n">
-        <v>4</v>
-      </c>
       <c r="H6" t="n">
-        <v>5</v>
+        <v>4.7</v>
       </c>
       <c r="I6" t="n">
-        <v>12</v>
+        <v>14.3</v>
       </c>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="n">
-        <v>-2</v>
+        <v>-0.5</v>
       </c>
       <c r="M6" t="inlineStr"/>
     </row>
@@ -1162,13 +1162,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>23.2</v>
+        <v>26.3</v>
       </c>
       <c r="C7" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="D7" t="n">
-        <v>8</v>
+        <v>4.5</v>
       </c>
       <c r="E7" t="n">
         <v>29.3</v>
@@ -1180,15 +1180,15 @@
         <v>21</v>
       </c>
       <c r="H7" t="n">
-        <v>24.5</v>
+        <v>22</v>
       </c>
       <c r="I7" t="n">
-        <v>14.5</v>
+        <v>10</v>
       </c>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="n">
-        <v>-3</v>
+        <v>-6</v>
       </c>
       <c r="M7" t="inlineStr"/>
     </row>
@@ -1199,13 +1199,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="C8" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D8" t="n">
-        <v>6</v>
+        <v>4.5</v>
       </c>
       <c r="E8" t="n">
         <v>22</v>
@@ -1217,15 +1217,15 @@
         <v>11</v>
       </c>
       <c r="H8" t="n">
-        <v>9.5</v>
+        <v>8</v>
       </c>
       <c r="I8" t="n">
-        <v>8.5</v>
+        <v>6.7</v>
       </c>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="n">
-        <v>-5</v>
+        <v>-6</v>
       </c>
       <c r="M8" t="inlineStr"/>
     </row>
@@ -1236,13 +1236,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>20</v>
+        <v>18.4</v>
       </c>
       <c r="C9" t="n">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="D9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E9" t="n">
         <v>23.4</v>
@@ -1254,15 +1254,15 @@
         <v>1</v>
       </c>
       <c r="H9" t="n">
-        <v>6.5</v>
+        <v>5</v>
       </c>
       <c r="I9" t="n">
-        <v>0.5</v>
+        <v>1.7</v>
       </c>
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="n">
-        <v>-7</v>
+        <v>-7.5</v>
       </c>
       <c r="M9" t="inlineStr"/>
     </row>
@@ -1373,25 +1373,25 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F2" t="n">
-        <v>43</v>
+        <v>60</v>
       </c>
       <c r="G2" t="n">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="H2" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="I2" t="n">
-        <v>21.5</v>
+        <v>20</v>
       </c>
       <c r="J2" t="n">
-        <v>20</v>
+        <v>17.3</v>
       </c>
       <c r="K2" t="n">
-        <v>1.5</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="3">
@@ -1416,25 +1416,25 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F3" t="n">
-        <v>46</v>
+        <v>66</v>
       </c>
       <c r="G3" t="n">
-        <v>26</v>
+        <v>43</v>
       </c>
       <c r="H3" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="I3" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="J3" t="n">
-        <v>13</v>
+        <v>14.3</v>
       </c>
       <c r="K3" t="n">
-        <v>10</v>
+        <v>7.7</v>
       </c>
     </row>
     <row r="4">
@@ -1459,25 +1459,25 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F4" t="n">
-        <v>53</v>
+        <v>78</v>
       </c>
       <c r="G4" t="n">
-        <v>29</v>
+        <v>52</v>
       </c>
       <c r="H4" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="I4" t="n">
-        <v>26.5</v>
+        <v>26</v>
       </c>
       <c r="J4" t="n">
-        <v>14.5</v>
+        <v>17.3</v>
       </c>
       <c r="K4" t="n">
-        <v>12</v>
+        <v>8.699999999999999</v>
       </c>
     </row>
     <row r="5">
@@ -1502,25 +1502,25 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F5" t="n">
-        <v>41</v>
+        <v>57</v>
       </c>
       <c r="G5" t="n">
-        <v>59</v>
+        <v>76</v>
       </c>
       <c r="H5" t="n">
-        <v>-18</v>
+        <v>-19</v>
       </c>
       <c r="I5" t="n">
-        <v>20.5</v>
+        <v>19</v>
       </c>
       <c r="J5" t="n">
-        <v>29.5</v>
+        <v>25.3</v>
       </c>
       <c r="K5" t="n">
-        <v>-9</v>
+        <v>-6.3</v>
       </c>
     </row>
   </sheetData>
@@ -1651,52 +1651,52 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C2" t="n">
-        <v>6</v>
+        <v>4.7</v>
       </c>
       <c r="D2" t="n">
-        <v>6</v>
+        <v>4.7</v>
       </c>
       <c r="E2" t="n">
-        <v>1.5</v>
+        <v>3.7</v>
       </c>
       <c r="F2" t="n">
-        <v>2</v>
+        <v>2.3</v>
       </c>
       <c r="G2" t="n">
-        <v>2.5</v>
+        <v>1.7</v>
       </c>
       <c r="H2" t="n">
-        <v>2</v>
+        <v>1.3</v>
       </c>
       <c r="I2" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="J2" t="n">
         <v>0</v>
       </c>
       <c r="K2" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="L2" t="n">
-        <v>1.5</v>
+        <v>1.3</v>
       </c>
       <c r="M2" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="N2" t="n">
         <v>1</v>
       </c>
       <c r="O2" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="P2" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="3">
@@ -1706,28 +1706,28 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="C3" t="n">
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>1.5</v>
+        <v>2.3</v>
       </c>
       <c r="E3" t="n">
-        <v>4.5</v>
+        <v>3</v>
       </c>
       <c r="F3" t="n">
-        <v>3.5</v>
+        <v>3</v>
       </c>
       <c r="G3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H3" t="n">
         <v>3</v>
       </c>
       <c r="I3" t="n">
-        <v>1</v>
+        <v>1.7</v>
       </c>
       <c r="J3" t="n">
         <v>0</v>
@@ -1736,22 +1736,22 @@
         <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="M3" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="N3" t="n">
-        <v>2</v>
+        <v>1.3</v>
       </c>
       <c r="O3" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="P3" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="4">
@@ -1761,29 +1761,29 @@
         </is>
       </c>
       <c r="B4" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="C4" t="n">
         <v>1</v>
       </c>
-      <c r="C4" t="n">
-        <v>0</v>
-      </c>
       <c r="D4" t="n">
-        <v>6</v>
+        <v>4.7</v>
       </c>
       <c r="E4" t="n">
-        <v>2.5</v>
+        <v>1.7</v>
       </c>
       <c r="F4" t="n">
         <v>0</v>
       </c>
       <c r="G4" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="H4" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="I4" t="n">
         <v>1</v>
       </c>
-      <c r="H4" t="n">
-        <v>2</v>
-      </c>
-      <c r="I4" t="n">
-        <v>1.5</v>
-      </c>
       <c r="J4" t="n">
         <v>0</v>
       </c>
@@ -1797,13 +1797,13 @@
         <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
@@ -1812,50 +1812,50 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>R. Soeiro</t>
+          <t>R. Woods</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.5</v>
+        <v>3.3</v>
       </c>
       <c r="C5" t="n">
-        <v>3</v>
+        <v>1.3</v>
       </c>
       <c r="D5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E5" t="n">
-        <v>1.5</v>
+        <v>2.7</v>
       </c>
       <c r="F5" t="n">
-        <v>2.5</v>
+        <v>0.7</v>
       </c>
       <c r="G5" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="H5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I5" t="n">
         <v>1</v>
       </c>
       <c r="J5" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="K5" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="L5" t="n">
+        <v>2</v>
+      </c>
+      <c r="M5" t="n">
         <v>1</v>
       </c>
-      <c r="K5" t="n">
-        <v>1</v>
-      </c>
-      <c r="L5" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="M5" t="n">
-        <v>0</v>
-      </c>
       <c r="N5" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="O5" t="n">
-        <v>4</v>
+        <v>0.3</v>
       </c>
       <c r="P5" t="n">
         <v>0</v>
@@ -1867,50 +1867,50 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>R. Woods</t>
+          <t>N. Morais</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3</v>
+        <v>0.7</v>
       </c>
       <c r="C6" t="n">
-        <v>1</v>
+        <v>4.3</v>
       </c>
       <c r="D6" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="E6" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>1.5</v>
+        <v>0.3</v>
       </c>
       <c r="H6" t="n">
-        <v>0</v>
+        <v>0.7</v>
       </c>
       <c r="I6" t="n">
         <v>1</v>
       </c>
       <c r="J6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>3</v>
+        <v>0.3</v>
       </c>
       <c r="L6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N6" t="n">
         <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="P6" t="n">
         <v>0</v>
@@ -1922,105 +1922,105 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>L. Boyle</t>
+          <t>M. Monteiro</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2</v>
+        <v>0.3</v>
       </c>
       <c r="C7" t="n">
-        <v>1.5</v>
+        <v>3.7</v>
       </c>
       <c r="D7" t="n">
-        <v>3</v>
+        <v>1.3</v>
       </c>
       <c r="E7" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="F7" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="G7" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="H7" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="I7" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="J7" t="n">
-        <v>1</v>
+        <v>1.3</v>
       </c>
       <c r="K7" t="n">
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="P7" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>N. Morais</t>
+          <t>R. Soeiro</t>
         </is>
       </c>
       <c r="B8" t="n">
         <v>1</v>
       </c>
       <c r="C8" t="n">
-        <v>4.5</v>
+        <v>1.5</v>
       </c>
       <c r="D8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F8" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="G8" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="H8" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="I8" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="J8" t="n">
-        <v>0</v>
+        <v>0.7</v>
       </c>
       <c r="K8" t="n">
         <v>0.5</v>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="M8" t="n">
         <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P8" t="n">
         <v>0</v>
@@ -2032,53 +2032,53 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>M. Monteiro</t>
+          <t>L. Boyle</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.5</v>
+        <v>1.3</v>
       </c>
       <c r="C9" t="n">
-        <v>3.5</v>
+        <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E9" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="F9" t="n">
-        <v>1</v>
+        <v>0.3</v>
       </c>
       <c r="G9" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="H9" t="n">
         <v>1</v>
       </c>
       <c r="I9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J9" t="n">
-        <v>1.5</v>
+        <v>0.7</v>
       </c>
       <c r="K9" t="n">
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>1.5</v>
+        <v>0.3</v>
       </c>
       <c r="M9" t="n">
-        <v>2</v>
+        <v>0.3</v>
       </c>
       <c r="N9" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
@@ -2096,11 +2096,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G3"/>
+  <dimension ref="A1:G4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
-    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="23" customWidth="1" min="2" max="2"/>
     <col width="11" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
@@ -2203,8 +2203,37 @@
         <v>16</v>
       </c>
     </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>2922729</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>CD Póvoa / Esc Online</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Home</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>78</v>
+      </c>
+      <c r="F4" t="n">
+        <v>69</v>
+      </c>
+      <c r="G4" t="n">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:G3"/>
+  <autoFilter ref="A1:G4"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/site/leagues/betclic/2026_2027/xlsx/context_packs/context_pack_ADO.xlsx
+++ b/site/leagues/betclic/2026_2027/xlsx/context_packs/context_pack_ADO.xlsx
@@ -17,12 +17,12 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'overview'!$A$1:$C$14</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'context_alerts'!$A$1:$B$4</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'team_splits'!$A$1:$I$3</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'context_alerts'!$A$1:$B$6</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'team_splits'!$A$1:$I$4</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'key_players_context'!$A$1:$M$9</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'team_periods'!$A$1:$K$5</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'key_players_periods'!$A$1:$Q$9</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'game_log'!$A$1:$G$4</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'game_log'!$A$1:$G$5</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -498,7 +498,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="5">
@@ -528,7 +528,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7">
@@ -544,7 +544,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>75.0%</t>
         </is>
       </c>
     </row>
@@ -561,7 +561,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>81.3</t>
         </is>
       </c>
     </row>
@@ -578,7 +578,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>73.5</t>
+          <t>72.7</t>
         </is>
       </c>
     </row>
@@ -595,7 +595,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>13.5</t>
+          <t>8.7</t>
         </is>
       </c>
     </row>
@@ -629,7 +629,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>16.0</t>
+          <t>7.5</t>
         </is>
       </c>
     </row>
@@ -646,7 +646,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Q3 (8.7)</t>
+          <t>Q3 (7)</t>
         </is>
       </c>
     </row>
@@ -663,7 +663,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Q4 (-6.3)</t>
+          <t>Q4 (-5)</t>
         </is>
       </c>
     </row>
@@ -679,11 +679,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B4"/>
+  <dimension ref="A1:B6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="11" customWidth="1" min="1" max="1"/>
-    <col width="32" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="45" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -706,19 +706,19 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Diff médio casa: 11 | fora: 16</t>
+          <t>Diff médio casa: 11 | fora: 7.5</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>períodos</t>
+          <t>resultado</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Melhor período: Q3 (8.7)</t>
+          <t>Diff médio em vitórias: 13.5 | em derrotas: -1</t>
         </is>
       </c>
     </row>
@@ -730,12 +730,36 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Pior período: Q4 (-6.3)</t>
+          <t>Melhor período: Q3 (7)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>períodos</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Pior período: Q4 (-5)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>player swing</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>J. Palm sobe mais em vitórias (9 ppg).</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:B4"/>
+  <autoFilter ref="A1:B6"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -746,7 +770,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I3"/>
+  <dimension ref="A1:I4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -815,35 +839,35 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>W</t>
+          <t>L</t>
         </is>
       </c>
       <c r="C2" t="n">
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>87</v>
+        <v>70</v>
       </c>
       <c r="E2" t="n">
         <v>71</v>
       </c>
       <c r="F2" t="n">
-        <v>16</v>
+        <v>-1</v>
       </c>
       <c r="G2" t="n">
-        <v>87</v>
+        <v>70</v>
       </c>
       <c r="H2" t="n">
         <v>71</v>
       </c>
       <c r="I2" t="n">
-        <v>16</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Home</t>
+          <t>Away</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -852,29 +876,62 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>174</v>
+        <v>87</v>
       </c>
       <c r="E3" t="n">
-        <v>152</v>
+        <v>71</v>
       </c>
       <c r="F3" t="n">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="G3" t="n">
         <v>87</v>
       </c>
       <c r="H3" t="n">
+        <v>71</v>
+      </c>
+      <c r="I3" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Home</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>2</v>
+      </c>
+      <c r="D4" t="n">
+        <v>174</v>
+      </c>
+      <c r="E4" t="n">
+        <v>152</v>
+      </c>
+      <c r="F4" t="n">
+        <v>22</v>
+      </c>
+      <c r="G4" t="n">
+        <v>87</v>
+      </c>
+      <c r="H4" t="n">
         <v>76</v>
       </c>
-      <c r="I3" t="n">
+      <c r="I4" t="n">
         <v>11</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I3"/>
+  <autoFilter ref="A1:I4"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -973,76 +1030,88 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>R. Woods</t>
+          <t>J. Palm</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>18.3</v>
+        <v>23.6</v>
       </c>
       <c r="C2" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="D2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E2" t="n">
-        <v>22.8</v>
+        <v>16.9</v>
       </c>
       <c r="F2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G2" t="n">
-        <v>17</v>
+        <v>-5</v>
       </c>
       <c r="H2" t="n">
-        <v>7.3</v>
+        <v>13</v>
       </c>
       <c r="I2" t="n">
-        <v>10.3</v>
-      </c>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
+        <v>8</v>
+      </c>
+      <c r="J2" t="n">
+        <v>4</v>
+      </c>
+      <c r="K2" t="n">
+        <v>-5</v>
+      </c>
       <c r="L2" t="n">
-        <v>8</v>
-      </c>
-      <c r="M2" t="inlineStr"/>
+        <v>9</v>
+      </c>
+      <c r="M2" t="n">
+        <v>9</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>N. Morais</t>
+          <t>R. Soeiro</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>16.9</v>
+        <v>18.4</v>
       </c>
       <c r="C3" t="n">
-        <v>8.5</v>
+        <v>2.5</v>
       </c>
       <c r="D3" t="n">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="E3" t="n">
-        <v>17.2</v>
+        <v>16.2</v>
       </c>
       <c r="F3" t="n">
+        <v>5</v>
+      </c>
+      <c r="G3" t="n">
+        <v>2</v>
+      </c>
+      <c r="H3" t="n">
+        <v>5</v>
+      </c>
+      <c r="I3" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K3" t="n">
         <v>3</v>
       </c>
-      <c r="G3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H3" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="I3" t="n">
-        <v>8.699999999999999</v>
-      </c>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
       <c r="L3" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="M3" t="inlineStr"/>
+        <v>-2.5</v>
+      </c>
+      <c r="M3" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1060,13 +1129,13 @@
         <v>9</v>
       </c>
       <c r="E4" t="n">
-        <v>23.8</v>
+        <v>27.6</v>
       </c>
       <c r="F4" t="n">
-        <v>9</v>
+        <v>8.5</v>
       </c>
       <c r="G4" t="n">
-        <v>-7</v>
+        <v>-4</v>
       </c>
       <c r="H4" t="n">
         <v>11.3</v>
@@ -1074,197 +1143,233 @@
       <c r="I4" t="n">
         <v>3.7</v>
       </c>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
+      <c r="J4" t="n">
+        <v>8</v>
+      </c>
+      <c r="K4" t="n">
+        <v>-1</v>
+      </c>
       <c r="L4" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="M4" t="inlineStr"/>
+        <v>4</v>
+      </c>
+      <c r="M4" t="n">
+        <v>3.3</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>M. Monteiro</t>
+          <t>L. Boyle</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>21.6</v>
+        <v>20.1</v>
       </c>
       <c r="C5" t="n">
-        <v>6.5</v>
+        <v>4.5</v>
       </c>
       <c r="D5" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="E5" t="n">
-        <v>16.7</v>
+        <v>13.3</v>
       </c>
       <c r="F5" t="n">
-        <v>6</v>
+        <v>3.5</v>
       </c>
       <c r="G5" t="n">
-        <v>4</v>
+        <v>7.5</v>
       </c>
       <c r="H5" t="n">
-        <v>6.3</v>
+        <v>4.7</v>
       </c>
       <c r="I5" t="n">
-        <v>9.300000000000001</v>
-      </c>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
+        <v>14.3</v>
+      </c>
+      <c r="J5" t="n">
+        <v>2</v>
+      </c>
+      <c r="K5" t="n">
+        <v>-5</v>
+      </c>
       <c r="L5" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="M5" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="M5" t="n">
+        <v>2.7</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>L. Boyle</t>
+          <t>R. Woods</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>20.1</v>
+        <v>18.3</v>
       </c>
       <c r="C6" t="n">
-        <v>4.5</v>
+        <v>10</v>
       </c>
       <c r="D6" t="n">
-        <v>11.5</v>
+        <v>7</v>
       </c>
       <c r="E6" t="n">
-        <v>16.2</v>
+        <v>21.7</v>
       </c>
       <c r="F6" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="G6" t="n">
+        <v>12</v>
+      </c>
+      <c r="H6" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="I6" t="n">
+        <v>10.3</v>
+      </c>
+      <c r="J6" t="n">
         <v>5</v>
       </c>
-      <c r="G6" t="n">
-        <v>20</v>
-      </c>
-      <c r="H6" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="I6" t="n">
-        <v>14.3</v>
-      </c>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
+      <c r="K6" t="n">
+        <v>7</v>
+      </c>
       <c r="L6" t="n">
-        <v>-0.5</v>
-      </c>
-      <c r="M6" t="inlineStr"/>
+        <v>6.5</v>
+      </c>
+      <c r="M6" t="n">
+        <v>2.3</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>L. Ayers</t>
+          <t>J. Wood</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>26.3</v>
+        <v>18</v>
       </c>
       <c r="C7" t="n">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="D7" t="n">
         <v>4.5</v>
       </c>
       <c r="E7" t="n">
-        <v>29.3</v>
+        <v>24.9</v>
       </c>
       <c r="F7" t="n">
-        <v>26</v>
+        <v>10</v>
       </c>
       <c r="G7" t="n">
-        <v>21</v>
+        <v>5.5</v>
       </c>
       <c r="H7" t="n">
-        <v>22</v>
+        <v>8</v>
       </c>
       <c r="I7" t="n">
-        <v>10</v>
-      </c>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
+        <v>6.7</v>
+      </c>
+      <c r="J7" t="n">
+        <v>8</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0</v>
+      </c>
       <c r="L7" t="n">
-        <v>-6</v>
-      </c>
-      <c r="M7" t="inlineStr"/>
+        <v>-4</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>J. Wood</t>
+          <t>L. Ayers</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>18</v>
+        <v>26.3</v>
       </c>
       <c r="C8" t="n">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="D8" t="n">
         <v>4.5</v>
       </c>
       <c r="E8" t="n">
+        <v>31.3</v>
+      </c>
+      <c r="F8" t="n">
+        <v>25</v>
+      </c>
+      <c r="G8" t="n">
+        <v>14</v>
+      </c>
+      <c r="H8" t="n">
         <v>22</v>
       </c>
-      <c r="F8" t="n">
-        <v>12</v>
-      </c>
-      <c r="G8" t="n">
-        <v>11</v>
-      </c>
-      <c r="H8" t="n">
-        <v>8</v>
-      </c>
       <c r="I8" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
+        <v>10</v>
+      </c>
+      <c r="J8" t="n">
+        <v>24</v>
+      </c>
+      <c r="K8" t="n">
+        <v>7</v>
+      </c>
       <c r="L8" t="n">
-        <v>-6</v>
-      </c>
-      <c r="M8" t="inlineStr"/>
+        <v>-5</v>
+      </c>
+      <c r="M8" t="n">
+        <v>-2</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>R. Soeiro</t>
+          <t>M. Monteiro</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>18.4</v>
+        <v>21.6</v>
       </c>
       <c r="C9" t="n">
-        <v>2.5</v>
+        <v>6.5</v>
       </c>
       <c r="D9" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="E9" t="n">
-        <v>23.4</v>
+        <v>19.6</v>
       </c>
       <c r="F9" t="n">
-        <v>10</v>
+        <v>7.5</v>
       </c>
       <c r="G9" t="n">
-        <v>1</v>
+        <v>-4</v>
       </c>
       <c r="H9" t="n">
-        <v>5</v>
+        <v>6.3</v>
       </c>
       <c r="I9" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
+        <v>9.300000000000001</v>
+      </c>
+      <c r="J9" t="n">
+        <v>9</v>
+      </c>
+      <c r="K9" t="n">
+        <v>-12</v>
+      </c>
       <c r="L9" t="n">
-        <v>-7.5</v>
-      </c>
-      <c r="M9" t="inlineStr"/>
+        <v>-1</v>
+      </c>
+      <c r="M9" t="n">
+        <v>-2.7</v>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:M9"/>
@@ -1373,25 +1478,25 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F2" t="n">
-        <v>60</v>
+        <v>84</v>
       </c>
       <c r="G2" t="n">
-        <v>52</v>
+        <v>68</v>
       </c>
       <c r="H2" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="I2" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J2" t="n">
-        <v>17.3</v>
+        <v>17</v>
       </c>
       <c r="K2" t="n">
-        <v>2.7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3">
@@ -1416,25 +1521,25 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F3" t="n">
-        <v>66</v>
+        <v>78</v>
       </c>
       <c r="G3" t="n">
-        <v>43</v>
+        <v>65</v>
       </c>
       <c r="H3" t="n">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="I3" t="n">
-        <v>22</v>
+        <v>19.5</v>
       </c>
       <c r="J3" t="n">
-        <v>14.3</v>
+        <v>16.2</v>
       </c>
       <c r="K3" t="n">
-        <v>7.7</v>
+        <v>3.2</v>
       </c>
     </row>
     <row r="4">
@@ -1459,25 +1564,25 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F4" t="n">
-        <v>78</v>
+        <v>94</v>
       </c>
       <c r="G4" t="n">
-        <v>52</v>
+        <v>66</v>
       </c>
       <c r="H4" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="I4" t="n">
-        <v>26</v>
+        <v>23.5</v>
       </c>
       <c r="J4" t="n">
-        <v>17.3</v>
+        <v>16.5</v>
       </c>
       <c r="K4" t="n">
-        <v>8.699999999999999</v>
+        <v>7</v>
       </c>
     </row>
     <row r="5">
@@ -1502,25 +1607,25 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F5" t="n">
-        <v>57</v>
+        <v>75</v>
       </c>
       <c r="G5" t="n">
-        <v>76</v>
+        <v>95</v>
       </c>
       <c r="H5" t="n">
-        <v>-19</v>
+        <v>-20</v>
       </c>
       <c r="I5" t="n">
-        <v>19</v>
+        <v>18.8</v>
       </c>
       <c r="J5" t="n">
-        <v>25.3</v>
+        <v>23.8</v>
       </c>
       <c r="K5" t="n">
-        <v>-6.3</v>
+        <v>-5</v>
       </c>
     </row>
   </sheetData>
@@ -1651,52 +1756,52 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>9</v>
+        <v>8.5</v>
       </c>
       <c r="C2" t="n">
-        <v>4.7</v>
+        <v>4.2</v>
       </c>
       <c r="D2" t="n">
-        <v>4.7</v>
+        <v>5</v>
       </c>
       <c r="E2" t="n">
-        <v>3.7</v>
+        <v>4.8</v>
       </c>
       <c r="F2" t="n">
-        <v>2.3</v>
+        <v>1.8</v>
       </c>
       <c r="G2" t="n">
-        <v>1.7</v>
+        <v>1.5</v>
       </c>
       <c r="H2" t="n">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="I2" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="J2" t="n">
         <v>0</v>
       </c>
       <c r="K2" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="L2" t="n">
-        <v>1.3</v>
+        <v>1</v>
       </c>
       <c r="M2" t="n">
-        <v>0.3</v>
+        <v>0.8</v>
       </c>
       <c r="N2" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="O2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="P2" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="Q2" t="n">
         <v>1</v>
-      </c>
-      <c r="O2" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="P2" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>0.7</v>
       </c>
     </row>
     <row r="3">
@@ -1706,159 +1811,159 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="C3" t="n">
-        <v>5</v>
+        <v>4.5</v>
       </c>
       <c r="D3" t="n">
-        <v>2.3</v>
+        <v>2.5</v>
       </c>
       <c r="E3" t="n">
-        <v>3</v>
+        <v>2.8</v>
       </c>
       <c r="F3" t="n">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="G3" t="n">
         <v>2</v>
       </c>
       <c r="H3" t="n">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="I3" t="n">
-        <v>1.7</v>
+        <v>1.2</v>
       </c>
       <c r="J3" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="K3" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="L3" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="M3" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="N3" t="n">
-        <v>1.3</v>
+        <v>1</v>
       </c>
       <c r="O3" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="P3" t="n">
-        <v>0.7</v>
+        <v>1</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>J. Wood</t>
+          <t>J. Palm</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.7</v>
+        <v>2</v>
       </c>
       <c r="C4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>4.7</v>
+        <v>5.7</v>
       </c>
       <c r="E4" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="F4" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="G4" t="n">
+        <v>2</v>
+      </c>
+      <c r="H4" t="n">
         <v>1.7</v>
       </c>
-      <c r="F4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G4" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="H4" t="n">
-        <v>1.3</v>
-      </c>
       <c r="I4" t="n">
-        <v>1</v>
+        <v>1.7</v>
       </c>
       <c r="J4" t="n">
         <v>0</v>
       </c>
       <c r="K4" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="N4" t="n">
         <v>0</v>
       </c>
-      <c r="L4" t="n">
-        <v>0</v>
-      </c>
-      <c r="M4" t="n">
-        <v>0</v>
-      </c>
-      <c r="N4" t="n">
-        <v>0.3</v>
-      </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>0.7</v>
       </c>
       <c r="P4" t="n">
         <v>0.3</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>R. Woods</t>
+          <t>J. Wood</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3.3</v>
+        <v>1</v>
       </c>
       <c r="C5" t="n">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="D5" t="n">
+        <v>4</v>
+      </c>
+      <c r="E5" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G5" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="H5" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="J5" t="n">
         <v>0</v>
       </c>
-      <c r="E5" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="F5" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="G5" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="H5" t="n">
+      <c r="K5" t="n">
         <v>0</v>
       </c>
-      <c r="I5" t="n">
-        <v>1</v>
-      </c>
-      <c r="J5" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="K5" t="n">
-        <v>2.3</v>
-      </c>
       <c r="L5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="O5" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
@@ -1867,111 +1972,111 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>N. Morais</t>
+          <t>M. Monteiro</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="C6" t="n">
-        <v>4.3</v>
+        <v>3.2</v>
       </c>
       <c r="D6" t="n">
-        <v>1.7</v>
+        <v>2.2</v>
       </c>
       <c r="E6" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="J6" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="K6" t="n">
         <v>0</v>
       </c>
-      <c r="F6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G6" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="H6" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="I6" t="n">
+      <c r="L6" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="M6" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="O6" t="n">
         <v>1</v>
       </c>
-      <c r="J6" t="n">
-        <v>0</v>
-      </c>
-      <c r="K6" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="L6" t="n">
-        <v>0</v>
-      </c>
-      <c r="M6" t="n">
-        <v>0</v>
-      </c>
-      <c r="N6" t="n">
-        <v>0</v>
-      </c>
-      <c r="O6" t="n">
-        <v>0</v>
-      </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>M. Monteiro</t>
+          <t>R. Woods</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.3</v>
+        <v>3.8</v>
       </c>
       <c r="C7" t="n">
-        <v>3.7</v>
+        <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="E7" t="n">
+        <v>2</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="G7" t="n">
         <v>1</v>
       </c>
-      <c r="F7" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="G7" t="n">
-        <v>0.3</v>
-      </c>
       <c r="H7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>0.3</v>
+        <v>0.8</v>
       </c>
       <c r="J7" t="n">
-        <v>1.3</v>
+        <v>1.8</v>
       </c>
       <c r="K7" t="n">
+        <v>2</v>
+      </c>
+      <c r="L7" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="M7" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="P7" t="n">
         <v>0</v>
       </c>
-      <c r="L7" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="M7" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="N7" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="O7" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="P7" t="n">
-        <v>0.3</v>
-      </c>
       <c r="Q7" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -1981,49 +2086,49 @@
         </is>
       </c>
       <c r="B8" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="C8" t="n">
         <v>1</v>
       </c>
-      <c r="C8" t="n">
+      <c r="D8" t="n">
         <v>1.5</v>
-      </c>
-      <c r="D8" t="n">
-        <v>2</v>
       </c>
       <c r="E8" t="n">
         <v>1</v>
       </c>
       <c r="F8" t="n">
-        <v>2.3</v>
+        <v>2</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
       </c>
       <c r="H8" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="I8" t="n">
         <v>0.7</v>
       </c>
       <c r="J8" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="K8" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="L8" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="M8" t="n">
         <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="O8" t="n">
-        <v>2</v>
+        <v>1.7</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
@@ -2036,52 +2141,52 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1.3</v>
+        <v>1.5</v>
       </c>
       <c r="C9" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="D9" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="E9" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="F9" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="G9" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="H9" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="I9" t="n">
         <v>1</v>
       </c>
       <c r="J9" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="K9" t="n">
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="M9" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="N9" t="n">
         <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="P9" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
     </row>
   </sheetData>
@@ -2096,11 +2201,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G4"/>
+  <dimension ref="A1:G5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
-    <col width="23" customWidth="1" min="2" max="2"/>
+    <col width="25" customWidth="1" min="2" max="2"/>
     <col width="11" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
@@ -2232,8 +2337,37 @@
         <v>9</v>
       </c>
     </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>2922736</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Sporting Clube Portugal</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Away</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>70</v>
+      </c>
+      <c r="F5" t="n">
+        <v>71</v>
+      </c>
+      <c r="G5" t="n">
+        <v>-1</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:G4"/>
+  <autoFilter ref="A1:G5"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>